--- a/data/trans_orig/IP12-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>14813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94503</t>
+          <t>93719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101634</t>
+          <t>101348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82847</t>
+          <t>82732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92323</t>
+          <t>92180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180379</t>
+          <t>180051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191883</t>
+          <t>192292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>75925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84257</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75005</t>
+          <t>75147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83057</t>
+          <t>83132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154042</t>
+          <t>154569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165068</t>
+          <t>165915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58848</t>
+          <t>58670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65532</t>
+          <t>65513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86710</t>
+          <t>86995</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95815</t>
+          <t>95940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149147</t>
+          <t>149183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159841</t>
+          <t>160025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>19763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>38889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180241</t>
+          <t>180970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191570</t>
+          <t>192389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179874</t>
+          <t>180524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192093</t>
+          <t>192511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364348</t>
+          <t>363918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381323</t>
+          <t>381005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90218</t>
+          <t>90600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99582</t>
+          <t>99939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115913</t>
+          <t>116654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124189</t>
+          <t>124511</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209956</t>
+          <t>210500</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222500</t>
+          <t>222825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11863</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68538</t>
+          <t>67942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74200</t>
+          <t>74190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64697</t>
+          <t>64316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71078</t>
+          <t>71095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>135432</t>
+          <t>135399</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>143906</t>
+          <t>144009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52207</t>
+          <t>51120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58274</t>
+          <t>58068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74664</t>
+          <t>75103</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>104201</t>
+          <t>104622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>586649</t>
+          <t>587736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>607022</t>
+          <t>606401</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626329</t>
+          <t>626535</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>646972</t>
+          <t>646758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1219258</t>
+          <t>1218837</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1248795</t>
+          <t>1248356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22514</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76374</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85396</t>
+          <t>85652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77546</t>
+          <t>77488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86684</t>
+          <t>86498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157183</t>
+          <t>156694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169928</t>
+          <t>169982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25068</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74640</t>
+          <t>75199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85733</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86024</t>
+          <t>86210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94212</t>
+          <t>94143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164976</t>
+          <t>165050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178210</t>
+          <t>178341</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>23188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73313</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82137</t>
+          <t>82080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73693</t>
+          <t>73566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82546</t>
+          <t>82301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150913</t>
+          <t>149859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162930</t>
+          <t>162728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24658</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>51519</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181450</t>
+          <t>181406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195174</t>
+          <t>194767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196221</t>
+          <t>197047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>212516</t>
+          <t>212303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382919</t>
+          <t>382694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403784</t>
+          <t>403561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130141</t>
+          <t>130214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>142010</t>
+          <t>141633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125258</t>
+          <t>125556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135449</t>
+          <t>135450</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>260237</t>
+          <t>259690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274627</t>
+          <t>274898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47667</t>
+          <t>47268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>53107</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62587</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112194</t>
+          <t>112735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122631</t>
+          <t>122991</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49071</t>
+          <t>49423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73808</t>
+          <t>74851</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47118</t>
+          <t>46986</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71011</t>
+          <t>71504</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104576</t>
+          <t>101384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138196</t>
+          <t>136307</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>604736</t>
+          <t>603693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>629473</t>
+          <t>629121</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>645622</t>
+          <t>645129</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>669515</t>
+          <t>669647</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256981</t>
+          <t>1258870</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1290601</t>
+          <t>1293793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>20365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68308</t>
+          <t>68007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77601</t>
+          <t>77512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91900</t>
+          <t>91755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98482</t>
+          <t>98390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162683</t>
+          <t>162522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174290</t>
+          <t>174208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19912</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95780</t>
+          <t>95116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102803</t>
+          <t>102784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98643</t>
+          <t>98794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107921</t>
+          <t>108075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>197931</t>
+          <t>197379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208831</t>
+          <t>209066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>15219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>53019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59811</t>
+          <t>59922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65559</t>
+          <t>65212</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73553</t>
+          <t>73019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121664</t>
+          <t>122049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131906</t>
+          <t>131814</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>49851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195624</t>
+          <t>195347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209247</t>
+          <t>209051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185243</t>
+          <t>185592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>198513</t>
+          <t>198713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386698</t>
+          <t>384580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404396</t>
+          <t>405052</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120079</t>
+          <t>119959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129914</t>
+          <t>130484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130915</t>
+          <t>130092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139321</t>
+          <t>139025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254070</t>
+          <t>253109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267262</t>
+          <t>267034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53925</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59752</t>
+          <t>59960</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66254</t>
+          <t>66535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115331</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124983</t>
+          <t>125297</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42780</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65769</t>
+          <t>65515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36089</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57835</t>
+          <t>58358</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85291</t>
+          <t>83702</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115448</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>605116</t>
+          <t>605370</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>628105</t>
+          <t>629443</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>651902</t>
+          <t>651379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673648</t>
+          <t>674192</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1265174</t>
+          <t>1264975</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1295331</t>
+          <t>1296920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>17083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>26470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87397</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97922</t>
+          <t>98043</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>124805</t>
+          <t>124674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134502</t>
+          <t>134117</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216204</t>
+          <t>214900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>230193</t>
+          <t>229824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85784</t>
+          <t>85952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92828</t>
+          <t>92799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>78820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89781</t>
+          <t>90030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168373</t>
+          <t>167994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181031</t>
+          <t>181089</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>45066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50545</t>
+          <t>50598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54132</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61677</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102445</t>
+          <t>102392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111392</t>
+          <t>111875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22596</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33919</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201833</t>
+          <t>201644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212860</t>
+          <t>212925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195676</t>
+          <t>194814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208847</t>
+          <t>208888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>402363</t>
+          <t>402357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>419502</t>
+          <t>419653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20202</t>
+          <t>19733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25842</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39546</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99226</t>
+          <t>99695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110593</t>
+          <t>110795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136775</t>
+          <t>137436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153043</t>
+          <t>153324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242499</t>
+          <t>242017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261237</t>
+          <t>261417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>66896</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>62724</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70525</t>
+          <t>70156</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126101</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>136340</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36330</t>
+          <t>35593</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58060</t>
+          <t>58583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>43642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71301</t>
+          <t>71139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87223</t>
+          <t>85154</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121286</t>
+          <t>121095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>599277</t>
+          <t>598754</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>621007</t>
+          <t>621744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677924</t>
+          <t>678086</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>704981</t>
+          <t>705583</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1285277</t>
+          <t>1285468</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1319340</t>
+          <t>1321409</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
